--- a/data/audits.xlsx
+++ b/data/audits.xlsx
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45852</v>
+        <v>45855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46128</v>
+        <v>46131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45872</v>
+        <v>45875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45963</v>
+        <v>45966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45921</v>
+        <v>45924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45860</v>
+        <v>45863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46042</v>
+        <v>46045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
